--- a/internal_doc/05.测试设计/story/事务支持RC隔离级别/测试场景.xlsx
+++ b/internal_doc/05.测试设计/story/事务支持RC隔离级别/测试场景.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="隔离级别基本测试场景" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="906" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="954" uniqueCount="264">
   <si>
     <t>操作步骤</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -764,10 +764,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>用例2：插入与更新并发</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>读到R1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -875,10 +871,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>用例3：插入与删除并发</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t>1.</t>
     </r>
@@ -1211,10 +1203,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>用例1：插入并发，过程中读</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t>7.</t>
     </r>
@@ -1955,38 +1943,6 @@
   </si>
   <si>
     <t>步骤3中的更新返回，未更新记录，读不到R1及R2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>用例4：更新并发-匹配更新前记录</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>用例5：更新并发-匹配更新后记录</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>用例6：更新与插入并发</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>用例7：更新与删除并发--匹配更新前记录</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>用例8：更新与删除并发--匹配更新后记录</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>用例9：删除并发</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>用例10：删除与插入并发</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>用例11：删除与更新并发</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2250,10 +2206,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>索引创建成功</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>报错-38，事务回滚失败？？？</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3888,6 +3840,1059 @@
   </si>
   <si>
     <t>读到步骤2中更新后的记录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>索引创建失败</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>场景1：插入并发，过程中读</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>场景2：插入与更新并发</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>场景3：插入与删除并发</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>场景4：更新并发-匹配更新前记录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>场景5：更新并发-匹配更新后记录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>场景6：更新与插入并发</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>场景7：更新与删除并发--匹配更新前记录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>场景8：更新与删除并发--匹配更新后记录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>场景9：删除并发</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>场景10：删除与插入并发</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>场景11：删除与更新并发</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>集合中已存在记录</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>R1</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>读到R1，不放锁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>3.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>事务</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>索引读</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>记录读</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>R1</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>事务</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>索引读</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>记录读</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>R1</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>集合中已存在记录</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>R1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（通过</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>mysql</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>测试）</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>事务</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>使用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>select for update</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>索引读</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>记录读记录</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>R1</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>场景12：读并发与更新并发</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>4.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>事务</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>更新记录</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>R1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>为</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>R2</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>事务3返回结果，R1更新为R2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>R1更新为R2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>3.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>事务</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>使用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>select for update</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>索引读</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>记录读记录</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>R1</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>5.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>事务</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>及事务</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>均提交</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>4.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>事务</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>删除记录</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>R1</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>R1删除成功</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>4.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>事务</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>更新记录</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>R1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>为</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>R2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>5.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>提交事务</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，记录读</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>索引读</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>5.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>回滚事务</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，记录读</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>索引读</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>4.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>事务</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>删除</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>R1</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>事务3返回结果，R1删除成功</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>集合中已存在记录</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>R1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（通过</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>mysql</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>测试或者驱动进行测试）</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>场景14：并发读写不同记录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>事务</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>插入记录</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>3.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>事务</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>更新记录</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>4.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>事务</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>删除记录</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>5.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>事务</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>索引读记录</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6.事务5记录读记录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>集合中已存在部分记录，并发执行如下事务操作</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>成功，立即返回</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>场景13：读并发与删除并发(RC隔离级别)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3938,7 +4943,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -3977,6 +4982,19 @@
     <border>
       <left/>
       <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -4035,7 +5053,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4050,7 +5068,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4059,7 +5077,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4068,7 +5086,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -4080,19 +5098,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -4101,12 +5122,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4412,13 +5449,13 @@
   <sheetData>
     <row r="1" spans="1:4" ht="30" customHeight="1">
       <c r="A1" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="B1" s="21" t="s">
+        <v>187</v>
+      </c>
+      <c r="B1" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
     </row>
     <row r="2" spans="1:4" ht="30" customHeight="1">
       <c r="A2" s="3" t="s">
@@ -4444,7 +5481,7 @@
     </row>
     <row r="4" spans="1:4" ht="30" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -4460,7 +5497,7 @@
     </row>
     <row r="6" spans="1:4" ht="30" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>10</v>
@@ -4484,7 +5521,7 @@
     </row>
     <row r="8" spans="1:4" ht="30" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -4493,7 +5530,7 @@
     <row r="9" spans="1:4" ht="30" customHeight="1"/>
     <row r="10" spans="1:4" ht="30" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="B10" s="14" t="s">
         <v>2</v>
@@ -4525,7 +5562,7 @@
     </row>
     <row r="13" spans="1:4" ht="30" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
@@ -4541,7 +5578,7 @@
     </row>
     <row r="15" spans="1:4" ht="30" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>9</v>
@@ -4565,7 +5602,7 @@
     </row>
     <row r="17" spans="1:4" ht="30" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
@@ -4574,7 +5611,7 @@
     <row r="18" spans="1:4" ht="30" customHeight="1"/>
     <row r="19" spans="1:4" ht="30" customHeight="1">
       <c r="A19" s="3" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="B19" s="14" t="s">
         <v>2</v>
@@ -4606,7 +5643,7 @@
     </row>
     <row r="22" spans="1:4" ht="30" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
@@ -4622,7 +5659,7 @@
     </row>
     <row r="24" spans="1:4" ht="30" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>13</v>
@@ -4646,7 +5683,7 @@
     </row>
     <row r="26" spans="1:4" ht="30" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
@@ -4655,7 +5692,7 @@
     <row r="27" spans="1:4" ht="30" customHeight="1"/>
     <row r="28" spans="1:4" ht="30" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="B28" s="14" t="s">
         <v>2</v>
@@ -4687,7 +5724,7 @@
     </row>
     <row r="31" spans="1:4" ht="30" customHeight="1">
       <c r="A31" s="2" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
@@ -4703,7 +5740,7 @@
     </row>
     <row r="33" spans="1:4" ht="30" customHeight="1">
       <c r="A33" s="2" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>15</v>
@@ -4727,7 +5764,7 @@
     </row>
     <row r="35" spans="1:4" ht="30" customHeight="1">
       <c r="A35" s="2" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
@@ -4736,7 +5773,7 @@
     <row r="36" spans="1:4" ht="30" customHeight="1"/>
     <row r="37" spans="1:4" ht="30" customHeight="1">
       <c r="A37" s="3" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="B37" s="14" t="s">
         <v>2</v>
@@ -4768,7 +5805,7 @@
     </row>
     <row r="40" spans="1:4" ht="30" customHeight="1">
       <c r="A40" s="2" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
@@ -4784,7 +5821,7 @@
     </row>
     <row r="42" spans="1:4" ht="30" customHeight="1">
       <c r="A42" s="2" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>15</v>
@@ -4808,7 +5845,7 @@
     </row>
     <row r="44" spans="1:4" ht="30" customHeight="1">
       <c r="A44" s="2" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
@@ -4817,7 +5854,7 @@
     <row r="45" spans="1:4" ht="30" customHeight="1"/>
     <row r="46" spans="1:4" ht="30" customHeight="1">
       <c r="A46" s="3" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="B46" s="14" t="s">
         <v>2</v>
@@ -4841,7 +5878,7 @@
     </row>
     <row r="48" spans="1:4" ht="30" customHeight="1">
       <c r="A48" s="2" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
@@ -4849,35 +5886,35 @@
     </row>
     <row r="49" spans="1:4" ht="30" customHeight="1">
       <c r="A49" s="2" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="30" customHeight="1">
       <c r="A50" s="2" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="30" customHeight="1">
       <c r="A51" s="2" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
@@ -4885,7 +5922,7 @@
     </row>
     <row r="52" spans="1:4" ht="30" customHeight="1">
       <c r="A52" s="2" t="s">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="B52" s="4"/>
       <c r="C52" s="4"/>
@@ -4894,7 +5931,7 @@
     <row r="53" spans="1:4" ht="30" customHeight="1"/>
     <row r="54" spans="1:4" ht="30" customHeight="1">
       <c r="A54" s="3" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="B54" s="14" t="s">
         <v>2</v>
@@ -4918,7 +5955,7 @@
     </row>
     <row r="56" spans="1:4" ht="30" customHeight="1">
       <c r="A56" s="2" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="B56" s="4"/>
       <c r="C56" s="4"/>
@@ -4926,35 +5963,35 @@
     </row>
     <row r="57" spans="1:4" ht="30" customHeight="1">
       <c r="A57" s="2" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="30" customHeight="1">
       <c r="A58" s="2" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="30" customHeight="1">
       <c r="A59" s="2" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="B59" s="4"/>
       <c r="C59" s="4"/>
@@ -4962,7 +5999,7 @@
     </row>
     <row r="60" spans="1:4" ht="30" customHeight="1">
       <c r="A60" s="2" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="B60" s="4"/>
       <c r="C60" s="4"/>
@@ -4971,7 +6008,7 @@
     <row r="61" spans="1:4" ht="30" customHeight="1"/>
     <row r="62" spans="1:4" ht="30" customHeight="1">
       <c r="A62" s="3" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="B62" s="14" t="s">
         <v>2</v>
@@ -4995,7 +6032,7 @@
     </row>
     <row r="64" spans="1:4" ht="30" customHeight="1">
       <c r="A64" s="2" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="B64" s="4"/>
       <c r="C64" s="4"/>
@@ -5003,35 +6040,35 @@
     </row>
     <row r="65" spans="1:4" ht="30" customHeight="1">
       <c r="A65" s="2" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="30" customHeight="1">
       <c r="A66" s="2" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="30" customHeight="1">
       <c r="A67" s="2" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="B67" s="4"/>
       <c r="C67" s="4"/>
@@ -5039,7 +6076,7 @@
     </row>
     <row r="68" spans="1:4" ht="30" customHeight="1">
       <c r="A68" s="2" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="B68" s="4"/>
       <c r="C68" s="4"/>
@@ -5048,7 +6085,7 @@
     <row r="69" spans="1:4" ht="30" customHeight="1"/>
     <row r="70" spans="1:4" ht="30" customHeight="1">
       <c r="A70" s="3" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="B70" s="14" t="s">
         <v>2</v>
@@ -5072,7 +6109,7 @@
     </row>
     <row r="72" spans="1:4" ht="30" customHeight="1">
       <c r="A72" s="2" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="B72" s="4"/>
       <c r="C72" s="4"/>
@@ -5080,7 +6117,7 @@
     </row>
     <row r="73" spans="1:4" ht="30" customHeight="1">
       <c r="A73" s="2" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="B73" s="4"/>
       <c r="C73" s="4"/>
@@ -5088,21 +6125,21 @@
     </row>
     <row r="74" spans="1:4" ht="30" customHeight="1">
       <c r="A74" s="2" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="30" customHeight="1">
       <c r="A75" s="2" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="B75" s="4"/>
       <c r="C75" s="4"/>
@@ -5110,7 +6147,7 @@
     </row>
     <row r="76" spans="1:4" ht="30" customHeight="1">
       <c r="A76" s="2" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="B76" s="4"/>
       <c r="C76" s="4"/>
@@ -5119,7 +6156,7 @@
     <row r="77" spans="1:4" ht="30" customHeight="1"/>
     <row r="78" spans="1:4" ht="30" customHeight="1">
       <c r="A78" s="3" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="B78" s="14" t="s">
         <v>2</v>
@@ -5143,7 +6180,7 @@
     </row>
     <row r="80" spans="1:4" ht="30" customHeight="1">
       <c r="A80" s="2" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="B80" s="4"/>
       <c r="C80" s="4"/>
@@ -5151,7 +6188,7 @@
     </row>
     <row r="81" spans="1:4" ht="30" customHeight="1">
       <c r="A81" s="2" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="B81" s="4"/>
       <c r="C81" s="4"/>
@@ -5159,21 +6196,21 @@
     </row>
     <row r="82" spans="1:4" ht="30" customHeight="1">
       <c r="A82" s="2" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
     </row>
     <row r="83" spans="1:4" ht="30" customHeight="1">
       <c r="A83" s="2" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="B83" s="4"/>
       <c r="C83" s="4"/>
@@ -5181,7 +6218,7 @@
     </row>
     <row r="84" spans="1:4" ht="30" customHeight="1">
       <c r="A84" s="2" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="B84" s="4"/>
       <c r="C84" s="4"/>
@@ -5228,22 +6265,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="30" customHeight="1">
-      <c r="A1" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
+      <c r="A1" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
     </row>
     <row r="2" spans="1:4" ht="30" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B2" s="21" t="s">
+        <v>224</v>
+      </c>
+      <c r="B2" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
     </row>
     <row r="3" spans="1:4" ht="30" customHeight="1">
       <c r="A3" s="3" t="s">
@@ -5291,7 +6328,7 @@
         <v>28</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>29</v>
@@ -5313,7 +6350,7 @@
     </row>
     <row r="9" spans="1:4" ht="30" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>28</v>
@@ -5327,7 +6364,7 @@
     </row>
     <row r="10" spans="1:4" ht="30" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>28</v>
@@ -5341,12 +6378,12 @@
     </row>
     <row r="11" spans="1:4" ht="30" customHeight="1">
       <c r="A11" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="22" t="s">
+      <c r="C11" s="23" t="s">
         <v>37</v>
       </c>
       <c r="D11" s="1" t="s">
@@ -5355,69 +6392,69 @@
     </row>
     <row r="12" spans="1:4" ht="30" customHeight="1">
       <c r="A12" s="7" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="22"/>
+      <c r="C12" s="23"/>
       <c r="D12" s="1" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="30" customHeight="1">
       <c r="A13" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="22"/>
+      <c r="C13" s="23"/>
       <c r="D13" s="1" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="30" customHeight="1">
       <c r="A14" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="22"/>
+      <c r="C14" s="23"/>
       <c r="D14" s="1" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="30" customHeight="1">
       <c r="A15" s="7" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C15" s="22"/>
+      <c r="C15" s="23"/>
       <c r="D15" s="1" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="30" customHeight="1">
-      <c r="A16" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="B16" s="17"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
+      <c r="A16" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="18"/>
     </row>
     <row r="17" spans="1:4" ht="30" customHeight="1">
       <c r="A17" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B17" s="21" t="s">
+        <v>225</v>
+      </c>
+      <c r="B17" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C17" s="21"/>
-      <c r="D17" s="21"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="22"/>
     </row>
     <row r="18" spans="1:4" ht="30" customHeight="1">
       <c r="A18" s="3" t="s">
@@ -5451,7 +6488,7 @@
     </row>
     <row r="21" spans="1:4" ht="30" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>6</v>
@@ -5468,13 +6505,13 @@
         <v>27</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="30" customHeight="1">
@@ -5487,10 +6524,10 @@
     </row>
     <row r="24" spans="1:4" ht="30" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>6</v>
@@ -5501,10 +6538,10 @@
     </row>
     <row r="25" spans="1:4" ht="30" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C25" s="9" t="s">
         <v>6</v>
@@ -5515,83 +6552,83 @@
     </row>
     <row r="26" spans="1:4" ht="30" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C26" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="C26" s="19" t="s">
         <v>36</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="30" customHeight="1">
       <c r="A27" s="7" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C27" s="19"/>
+        <v>41</v>
+      </c>
+      <c r="C27" s="20"/>
       <c r="D27" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="30" customHeight="1">
       <c r="A28" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C28" s="19"/>
+        <v>41</v>
+      </c>
+      <c r="C28" s="20"/>
       <c r="D28" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="30" customHeight="1">
       <c r="A29" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C29" s="19"/>
+        <v>41</v>
+      </c>
+      <c r="C29" s="20"/>
       <c r="D29" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="30" customHeight="1">
       <c r="A30" s="7" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C30" s="20"/>
+        <v>41</v>
+      </c>
+      <c r="C30" s="21"/>
       <c r="D30" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="30" customHeight="1">
-      <c r="A31" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="B31" s="17"/>
-      <c r="C31" s="17"/>
-      <c r="D31" s="17"/>
+      <c r="A31" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="B31" s="18"/>
+      <c r="C31" s="18"/>
+      <c r="D31" s="18"/>
     </row>
     <row r="32" spans="1:4" ht="30" customHeight="1">
       <c r="A32" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B32" s="21" t="s">
+        <v>226</v>
+      </c>
+      <c r="B32" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C32" s="21"/>
-      <c r="D32" s="21"/>
+      <c r="C32" s="22"/>
+      <c r="D32" s="22"/>
     </row>
     <row r="33" spans="1:4" ht="30" customHeight="1">
       <c r="A33" s="3" t="s">
@@ -5625,7 +6662,7 @@
     </row>
     <row r="36" spans="1:4" ht="30" customHeight="1">
       <c r="A36" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>6</v>
@@ -5642,13 +6679,13 @@
         <v>27</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="30" customHeight="1">
@@ -5661,111 +6698,111 @@
     </row>
     <row r="39" spans="1:4" ht="30" customHeight="1">
       <c r="A39" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="30" customHeight="1">
       <c r="A40" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C40" s="9" t="s">
         <v>6</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="30" customHeight="1">
       <c r="A41" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C41" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="C41" s="19" t="s">
         <v>36</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="30" customHeight="1">
       <c r="A42" s="7" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C42" s="19"/>
+        <v>46</v>
+      </c>
+      <c r="C42" s="20"/>
       <c r="D42" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="30" customHeight="1">
       <c r="A43" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C43" s="19"/>
+        <v>46</v>
+      </c>
+      <c r="C43" s="20"/>
       <c r="D43" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="30" customHeight="1">
       <c r="A44" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C44" s="19"/>
+        <v>46</v>
+      </c>
+      <c r="C44" s="20"/>
       <c r="D44" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="30" customHeight="1">
       <c r="A45" s="7" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C45" s="20"/>
+        <v>46</v>
+      </c>
+      <c r="C45" s="21"/>
       <c r="D45" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="30" customHeight="1">
-      <c r="A46" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="B46" s="17"/>
-      <c r="C46" s="17"/>
-      <c r="D46" s="17"/>
+      <c r="A46" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="B46" s="18"/>
+      <c r="C46" s="18"/>
+      <c r="D46" s="18"/>
     </row>
     <row r="47" spans="1:4" ht="30" customHeight="1">
       <c r="A47" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B47" s="21" t="s">
+        <v>227</v>
+      </c>
+      <c r="B47" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C47" s="21"/>
-      <c r="D47" s="21"/>
+      <c r="C47" s="22"/>
+      <c r="D47" s="22"/>
     </row>
     <row r="48" spans="1:4" ht="30" customHeight="1">
       <c r="A48" s="3" t="s">
@@ -5783,7 +6820,7 @@
     </row>
     <row r="49" spans="1:4" ht="30" customHeight="1">
       <c r="A49" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B49" s="4"/>
       <c r="C49" s="4"/>
@@ -5791,7 +6828,7 @@
     </row>
     <row r="50" spans="1:4" ht="30" customHeight="1">
       <c r="A50" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
@@ -5799,7 +6836,7 @@
     </row>
     <row r="51" spans="1:4" ht="30" customHeight="1">
       <c r="A51" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>6</v>
@@ -5816,13 +6853,13 @@
         <v>27</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C52" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="30" customHeight="1">
@@ -5835,111 +6872,111 @@
     </row>
     <row r="54" spans="1:4" ht="30" customHeight="1">
       <c r="A54" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C54" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="30" customHeight="1">
       <c r="A55" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C55" s="9" t="s">
         <v>6</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="30" customHeight="1">
       <c r="A56" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C56" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="C56" s="19" t="s">
         <v>36</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="30" customHeight="1">
       <c r="A57" s="7" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C57" s="19"/>
+        <v>41</v>
+      </c>
+      <c r="C57" s="20"/>
       <c r="D57" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="30" customHeight="1">
       <c r="A58" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C58" s="19"/>
+        <v>41</v>
+      </c>
+      <c r="C58" s="20"/>
       <c r="D58" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="30" customHeight="1">
       <c r="A59" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C59" s="19"/>
+        <v>41</v>
+      </c>
+      <c r="C59" s="20"/>
       <c r="D59" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="30" customHeight="1">
       <c r="A60" s="7" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C60" s="20"/>
+        <v>41</v>
+      </c>
+      <c r="C60" s="21"/>
       <c r="D60" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="30" customHeight="1">
-      <c r="A61" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="B61" s="17"/>
-      <c r="C61" s="17"/>
-      <c r="D61" s="17"/>
+      <c r="A61" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="B61" s="18"/>
+      <c r="C61" s="18"/>
+      <c r="D61" s="18"/>
     </row>
     <row r="62" spans="1:4" ht="30" customHeight="1">
       <c r="A62" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="B62" s="21" t="s">
+        <v>228</v>
+      </c>
+      <c r="B62" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C62" s="21"/>
-      <c r="D62" s="21"/>
+      <c r="C62" s="22"/>
+      <c r="D62" s="22"/>
     </row>
     <row r="63" spans="1:4" ht="30" customHeight="1">
       <c r="A63" s="3" t="s">
@@ -5957,7 +6994,7 @@
     </row>
     <row r="64" spans="1:4" ht="30" customHeight="1">
       <c r="A64" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B64" s="4"/>
       <c r="C64" s="4"/>
@@ -5965,7 +7002,7 @@
     </row>
     <row r="65" spans="1:4" ht="30" customHeight="1">
       <c r="A65" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B65" s="4"/>
       <c r="C65" s="4"/>
@@ -5973,16 +7010,16 @@
     </row>
     <row r="66" spans="1:4" ht="30" customHeight="1">
       <c r="A66" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="30" customHeight="1">
@@ -5990,13 +7027,13 @@
         <v>27</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C67" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="30" customHeight="1">
@@ -6009,111 +7046,111 @@
     </row>
     <row r="69" spans="1:4" ht="30" customHeight="1">
       <c r="A69" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C69" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="30" customHeight="1">
       <c r="A70" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C70" s="9" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="30" customHeight="1">
       <c r="A71" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C71" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="C71" s="19" t="s">
         <v>36</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="30" customHeight="1">
       <c r="A72" s="7" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C72" s="19"/>
+        <v>50</v>
+      </c>
+      <c r="C72" s="20"/>
       <c r="D72" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="73" spans="1:4" ht="30" customHeight="1">
       <c r="A73" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C73" s="19"/>
+        <v>50</v>
+      </c>
+      <c r="C73" s="20"/>
       <c r="D73" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="74" spans="1:4" ht="30" customHeight="1">
       <c r="A74" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C74" s="19"/>
+        <v>50</v>
+      </c>
+      <c r="C74" s="20"/>
       <c r="D74" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="30" customHeight="1">
       <c r="A75" s="7" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C75" s="20"/>
+        <v>50</v>
+      </c>
+      <c r="C75" s="21"/>
       <c r="D75" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="76" spans="1:4" ht="30" customHeight="1">
-      <c r="A76" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="B76" s="17"/>
-      <c r="C76" s="17"/>
-      <c r="D76" s="17"/>
+      <c r="A76" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="B76" s="18"/>
+      <c r="C76" s="18"/>
+      <c r="D76" s="18"/>
     </row>
     <row r="77" spans="1:4" ht="30" customHeight="1">
       <c r="A77" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="B77" s="21" t="s">
+        <v>229</v>
+      </c>
+      <c r="B77" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C77" s="21"/>
-      <c r="D77" s="21"/>
+      <c r="C77" s="22"/>
+      <c r="D77" s="22"/>
     </row>
     <row r="78" spans="1:4" ht="30" customHeight="1">
       <c r="A78" s="3" t="s">
@@ -6131,7 +7168,7 @@
     </row>
     <row r="79" spans="1:4" ht="30" customHeight="1">
       <c r="A79" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B79" s="4"/>
       <c r="C79" s="4"/>
@@ -6139,7 +7176,7 @@
     </row>
     <row r="80" spans="1:4" ht="30" customHeight="1">
       <c r="A80" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B80" s="4"/>
       <c r="C80" s="4"/>
@@ -6147,7 +7184,7 @@
     </row>
     <row r="81" spans="1:4" ht="30" customHeight="1">
       <c r="A81" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B81" s="4"/>
       <c r="C81" s="4"/>
@@ -6158,13 +7195,13 @@
         <v>27</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C82" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="83" spans="1:4" ht="30" customHeight="1">
@@ -6172,122 +7209,122 @@
         <v>33</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C83" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="84" spans="1:4" ht="30" customHeight="1">
       <c r="A84" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C84" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="85" spans="1:4" ht="30" customHeight="1">
       <c r="A85" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C85" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="86" spans="1:4" ht="30" customHeight="1">
       <c r="A86" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C86" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="C86" s="23" t="s">
         <v>36</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="87" spans="1:4" ht="30" customHeight="1">
       <c r="A87" s="7" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C87" s="22"/>
+        <v>53</v>
+      </c>
+      <c r="C87" s="23"/>
       <c r="D87" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="88" spans="1:4" ht="30" customHeight="1">
       <c r="A88" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C88" s="22"/>
+        <v>53</v>
+      </c>
+      <c r="C88" s="23"/>
       <c r="D88" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="89" spans="1:4" ht="30" customHeight="1">
       <c r="A89" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C89" s="22"/>
+        <v>53</v>
+      </c>
+      <c r="C89" s="23"/>
       <c r="D89" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="90" spans="1:4" ht="30" customHeight="1">
       <c r="A90" s="7" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C90" s="22"/>
+        <v>53</v>
+      </c>
+      <c r="C90" s="23"/>
       <c r="D90" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="91" spans="1:4" ht="30" customHeight="1">
-      <c r="A91" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="B91" s="17"/>
-      <c r="C91" s="17"/>
-      <c r="D91" s="17"/>
+      <c r="A91" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="B91" s="18"/>
+      <c r="C91" s="18"/>
+      <c r="D91" s="18"/>
     </row>
     <row r="92" spans="1:4" ht="30" customHeight="1">
       <c r="A92" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="B92" s="21" t="s">
+        <v>230</v>
+      </c>
+      <c r="B92" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C92" s="21"/>
-      <c r="D92" s="21"/>
+      <c r="C92" s="22"/>
+      <c r="D92" s="22"/>
     </row>
     <row r="93" spans="1:4" ht="30" customHeight="1">
       <c r="A93" s="3" t="s">
@@ -6305,7 +7342,7 @@
     </row>
     <row r="94" spans="1:4" ht="30" customHeight="1">
       <c r="A94" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B94" s="4"/>
       <c r="C94" s="4"/>
@@ -6313,7 +7350,7 @@
     </row>
     <row r="95" spans="1:4" ht="30" customHeight="1">
       <c r="A95" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B95" s="4"/>
       <c r="C95" s="4"/>
@@ -6321,7 +7358,7 @@
     </row>
     <row r="96" spans="1:4" ht="30" customHeight="1">
       <c r="A96" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B96" s="4" t="s">
         <v>6</v>
@@ -6338,13 +7375,13 @@
         <v>27</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C97" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="98" spans="1:4" ht="30" customHeight="1">
@@ -6357,111 +7394,111 @@
     </row>
     <row r="99" spans="1:4" ht="30" customHeight="1">
       <c r="A99" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C99" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="100" spans="1:4" ht="30" customHeight="1">
       <c r="A100" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C100" s="9" t="s">
         <v>6</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="101" spans="1:4" ht="30" customHeight="1">
       <c r="A101" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="C101" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="C101" s="19" t="s">
         <v>36</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="102" spans="1:4" ht="30" customHeight="1">
       <c r="A102" s="7" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C102" s="19"/>
+        <v>41</v>
+      </c>
+      <c r="C102" s="20"/>
       <c r="D102" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="103" spans="1:4" ht="30" customHeight="1">
       <c r="A103" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C103" s="19"/>
+        <v>41</v>
+      </c>
+      <c r="C103" s="20"/>
       <c r="D103" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="104" spans="1:4" ht="30" customHeight="1">
       <c r="A104" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C104" s="19"/>
+        <v>41</v>
+      </c>
+      <c r="C104" s="20"/>
       <c r="D104" s="1" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="105" spans="1:4" ht="30" customHeight="1">
       <c r="A105" s="7" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C105" s="20"/>
+        <v>41</v>
+      </c>
+      <c r="C105" s="21"/>
       <c r="D105" s="1" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="106" spans="1:4" ht="30" customHeight="1">
-      <c r="A106" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="B106" s="17"/>
-      <c r="C106" s="17"/>
-      <c r="D106" s="17"/>
+      <c r="A106" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="B106" s="18"/>
+      <c r="C106" s="18"/>
+      <c r="D106" s="18"/>
     </row>
     <row r="107" spans="1:4" ht="30" customHeight="1">
       <c r="A107" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="B107" s="21" t="s">
+        <v>231</v>
+      </c>
+      <c r="B107" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C107" s="21"/>
-      <c r="D107" s="21"/>
+      <c r="C107" s="22"/>
+      <c r="D107" s="22"/>
     </row>
     <row r="108" spans="1:4" ht="30" customHeight="1">
       <c r="A108" s="3" t="s">
@@ -6479,7 +7516,7 @@
     </row>
     <row r="109" spans="1:4" ht="30" customHeight="1">
       <c r="A109" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B109" s="4"/>
       <c r="C109" s="4"/>
@@ -6487,7 +7524,7 @@
     </row>
     <row r="110" spans="1:4" ht="30" customHeight="1">
       <c r="A110" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B110" s="4"/>
       <c r="C110" s="4"/>
@@ -6495,7 +7532,7 @@
     </row>
     <row r="111" spans="1:4" ht="30" customHeight="1">
       <c r="A111" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B111" s="4" t="s">
         <v>6</v>
@@ -6504,7 +7541,7 @@
         <v>6</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="112" spans="1:4" ht="30" customHeight="1">
@@ -6512,13 +7549,13 @@
         <v>27</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C112" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="113" spans="1:4" ht="30" customHeight="1">
@@ -6531,111 +7568,111 @@
     </row>
     <row r="114" spans="1:4" ht="30" customHeight="1">
       <c r="A114" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C114" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="115" spans="1:4" ht="30" customHeight="1">
       <c r="A115" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C115" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="116" spans="1:4" ht="30" customHeight="1">
       <c r="A116" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="C116" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="C116" s="19" t="s">
         <v>36</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="117" spans="1:4" ht="30" customHeight="1">
       <c r="A117" s="7" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B117" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C117" s="19"/>
+      <c r="C117" s="20"/>
       <c r="D117" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="118" spans="1:4" ht="30" customHeight="1">
       <c r="A118" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B118" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C118" s="19"/>
+      <c r="C118" s="20"/>
       <c r="D118" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="119" spans="1:4" ht="30" customHeight="1">
       <c r="A119" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B119" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C119" s="19"/>
+      <c r="C119" s="20"/>
       <c r="D119" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="120" spans="1:4" ht="30" customHeight="1">
       <c r="A120" s="7" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B120" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C120" s="20"/>
+      <c r="C120" s="21"/>
       <c r="D120" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="121" spans="1:4" ht="30" customHeight="1">
-      <c r="A121" s="16" t="s">
-        <v>99</v>
-      </c>
-      <c r="B121" s="17"/>
-      <c r="C121" s="17"/>
-      <c r="D121" s="17"/>
+      <c r="A121" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="B121" s="18"/>
+      <c r="C121" s="18"/>
+      <c r="D121" s="18"/>
     </row>
     <row r="122" spans="1:4" ht="30" customHeight="1">
       <c r="A122" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="B122" s="21" t="s">
+        <v>232</v>
+      </c>
+      <c r="B122" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C122" s="21"/>
-      <c r="D122" s="21"/>
+      <c r="C122" s="22"/>
+      <c r="D122" s="22"/>
     </row>
     <row r="123" spans="1:4" ht="30" customHeight="1">
       <c r="A123" s="3" t="s">
@@ -6653,7 +7690,7 @@
     </row>
     <row r="124" spans="1:4" ht="30" customHeight="1">
       <c r="A124" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B124" s="4"/>
       <c r="C124" s="4"/>
@@ -6661,7 +7698,7 @@
     </row>
     <row r="125" spans="1:4" ht="30" customHeight="1">
       <c r="A125" s="2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B125" s="4"/>
       <c r="C125" s="4"/>
@@ -6669,7 +7706,7 @@
     </row>
     <row r="126" spans="1:4" ht="30" customHeight="1">
       <c r="A126" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B126" s="4" t="s">
         <v>6</v>
@@ -6678,7 +7715,7 @@
         <v>6</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="127" spans="1:4" ht="30" customHeight="1">
@@ -6686,13 +7723,13 @@
         <v>27</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C127" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="128" spans="1:4" ht="30" customHeight="1">
@@ -6705,111 +7742,111 @@
     </row>
     <row r="129" spans="1:4" ht="30" customHeight="1">
       <c r="A129" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C129" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="130" spans="1:4" ht="30" customHeight="1">
       <c r="A130" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C130" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="131" spans="1:4" ht="30" customHeight="1">
       <c r="A131" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C131" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="C131" s="19" t="s">
         <v>36</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="132" spans="1:4" ht="30" customHeight="1">
       <c r="A132" s="7" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C132" s="19"/>
+        <v>46</v>
+      </c>
+      <c r="C132" s="20"/>
       <c r="D132" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="133" spans="1:4" ht="30" customHeight="1">
       <c r="A133" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C133" s="19"/>
+        <v>46</v>
+      </c>
+      <c r="C133" s="20"/>
       <c r="D133" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="134" spans="1:4" ht="30" customHeight="1">
       <c r="A134" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C134" s="19"/>
+        <v>46</v>
+      </c>
+      <c r="C134" s="20"/>
       <c r="D134" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="135" spans="1:4" ht="30" customHeight="1">
       <c r="A135" s="7" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C135" s="20"/>
+        <v>46</v>
+      </c>
+      <c r="C135" s="21"/>
       <c r="D135" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="136" spans="1:4" ht="30" customHeight="1">
-      <c r="A136" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="B136" s="17"/>
-      <c r="C136" s="17"/>
-      <c r="D136" s="17"/>
+      <c r="A136" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="B136" s="18"/>
+      <c r="C136" s="18"/>
+      <c r="D136" s="18"/>
     </row>
     <row r="137" spans="1:4" ht="30" customHeight="1">
       <c r="A137" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="B137" s="21" t="s">
+        <v>233</v>
+      </c>
+      <c r="B137" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C137" s="21"/>
-      <c r="D137" s="21"/>
+      <c r="C137" s="22"/>
+      <c r="D137" s="22"/>
     </row>
     <row r="138" spans="1:4" ht="30" customHeight="1">
       <c r="A138" s="3" t="s">
@@ -6827,7 +7864,7 @@
     </row>
     <row r="139" spans="1:4" ht="30" customHeight="1">
       <c r="A139" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B139" s="4"/>
       <c r="C139" s="4"/>
@@ -6835,7 +7872,7 @@
     </row>
     <row r="140" spans="1:4" ht="30" customHeight="1">
       <c r="A140" s="2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B140" s="4"/>
       <c r="C140" s="4"/>
@@ -6843,7 +7880,7 @@
     </row>
     <row r="141" spans="1:4" ht="30" customHeight="1">
       <c r="A141" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B141" s="4"/>
       <c r="C141" s="4"/>
@@ -6854,7 +7891,7 @@
         <v>27</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C142" s="4" t="s">
         <v>6</v>
@@ -6868,51 +7905,51 @@
         <v>33</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C143" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="144" spans="1:4" ht="30" customHeight="1">
       <c r="A144" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C144" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="145" spans="1:4" ht="30" customHeight="1">
       <c r="A145" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C145" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="146" spans="1:4" ht="30" customHeight="1">
       <c r="A146" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C146" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="C146" s="19" t="s">
         <v>36</v>
       </c>
       <c r="D146" s="4" t="s">
@@ -6921,69 +7958,69 @@
     </row>
     <row r="147" spans="1:4" ht="30" customHeight="1">
       <c r="A147" s="7" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C147" s="19"/>
+        <v>41</v>
+      </c>
+      <c r="C147" s="20"/>
       <c r="D147" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="148" spans="1:4" ht="30" customHeight="1">
       <c r="A148" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C148" s="19"/>
+        <v>41</v>
+      </c>
+      <c r="C148" s="20"/>
       <c r="D148" s="1" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="149" spans="1:4" ht="30" customHeight="1">
       <c r="A149" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C149" s="19"/>
+        <v>41</v>
+      </c>
+      <c r="C149" s="20"/>
       <c r="D149" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="150" spans="1:4" ht="30" customHeight="1">
       <c r="A150" s="7" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C150" s="20"/>
+        <v>41</v>
+      </c>
+      <c r="C150" s="21"/>
       <c r="D150" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="151" spans="1:4" ht="30" customHeight="1">
-      <c r="A151" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="B151" s="17"/>
-      <c r="C151" s="17"/>
-      <c r="D151" s="17"/>
+      <c r="A151" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="B151" s="18"/>
+      <c r="C151" s="18"/>
+      <c r="D151" s="18"/>
     </row>
     <row r="152" spans="1:4" ht="30" customHeight="1">
       <c r="A152" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="B152" s="21" t="s">
+        <v>234</v>
+      </c>
+      <c r="B152" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C152" s="21"/>
-      <c r="D152" s="21"/>
+      <c r="C152" s="22"/>
+      <c r="D152" s="22"/>
     </row>
     <row r="153" spans="1:4" ht="30" customHeight="1">
       <c r="A153" s="3" t="s">
@@ -7001,7 +8038,7 @@
     </row>
     <row r="154" spans="1:4" ht="30" customHeight="1">
       <c r="A154" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B154" s="4"/>
       <c r="C154" s="4"/>
@@ -7009,7 +8046,7 @@
     </row>
     <row r="155" spans="1:4" ht="30" customHeight="1">
       <c r="A155" s="2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B155" s="4"/>
       <c r="C155" s="4"/>
@@ -7017,7 +8054,7 @@
     </row>
     <row r="156" spans="1:4" ht="30" customHeight="1">
       <c r="A156" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B156" s="4" t="s">
         <v>6</v>
@@ -7053,7 +8090,7 @@
     </row>
     <row r="159" spans="1:4" ht="30" customHeight="1">
       <c r="A159" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B159" s="4" t="s">
         <v>32</v>
@@ -7062,12 +8099,12 @@
         <v>6</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="160" spans="1:4" ht="30" customHeight="1">
       <c r="A160" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B160" s="4" t="s">
         <v>32</v>
@@ -7076,98 +8113,315 @@
         <v>6</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="161" spans="1:4" ht="30" customHeight="1">
       <c r="A161" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="C161" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="C161" s="19" t="s">
         <v>36</v>
       </c>
       <c r="D161" s="4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="162" spans="1:4" ht="30" customHeight="1">
       <c r="A162" s="7" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B162" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C162" s="19"/>
+      <c r="C162" s="20"/>
       <c r="D162" s="4" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="163" spans="1:4" ht="30" customHeight="1">
       <c r="A163" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B163" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C163" s="19"/>
+      <c r="C163" s="20"/>
       <c r="D163" s="4" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="164" spans="1:4" ht="30" customHeight="1">
       <c r="A164" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B164" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C164" s="19"/>
+      <c r="C164" s="20"/>
       <c r="D164" s="4" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="165" spans="1:4" ht="30" customHeight="1">
       <c r="A165" s="7" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B165" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C165" s="20"/>
+      <c r="C165" s="21"/>
       <c r="D165" s="4" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="166" spans="1:4" ht="30" customHeight="1"/>
-    <row r="167" spans="1:4" ht="30" customHeight="1"/>
-    <row r="168" spans="1:4" ht="30" customHeight="1"/>
-    <row r="169" spans="1:4" ht="30" customHeight="1"/>
-    <row r="170" spans="1:4" ht="30" customHeight="1"/>
-    <row r="171" spans="1:4" ht="30" customHeight="1"/>
-    <row r="172" spans="1:4" ht="30" customHeight="1"/>
-    <row r="173" spans="1:4" ht="30" customHeight="1"/>
-    <row r="174" spans="1:4" ht="30" customHeight="1"/>
-    <row r="175" spans="1:4" ht="30" customHeight="1"/>
-    <row r="176" spans="1:4" ht="30" customHeight="1"/>
-    <row r="177" ht="30" customHeight="1"/>
-    <row r="178" ht="30" customHeight="1"/>
-    <row r="179" ht="30" customHeight="1"/>
-    <row r="180" ht="30" customHeight="1"/>
-    <row r="181" ht="30" customHeight="1"/>
-    <row r="182" ht="30" customHeight="1"/>
-    <row r="183" ht="30" customHeight="1"/>
-    <row r="184" ht="30" customHeight="1"/>
-    <row r="185" ht="30" customHeight="1"/>
-    <row r="186" ht="30" customHeight="1"/>
-    <row r="187" ht="30" customHeight="1"/>
-    <row r="188" ht="30" customHeight="1"/>
-    <row r="189" ht="30" customHeight="1"/>
-    <row r="190" ht="30" customHeight="1"/>
-    <row r="191" ht="30" customHeight="1"/>
-    <row r="192" ht="30" customHeight="1"/>
+    <row r="167" spans="1:4" ht="30" customHeight="1">
+      <c r="A167" s="26" t="s">
+        <v>241</v>
+      </c>
+      <c r="B167" s="29"/>
+      <c r="C167" s="29"/>
+      <c r="D167" s="27"/>
+    </row>
+    <row r="168" spans="1:4" ht="30" customHeight="1">
+      <c r="A168" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="B168" s="28" t="s">
+        <v>151</v>
+      </c>
+      <c r="C168" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="D168" s="28" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" ht="30" customHeight="1">
+      <c r="A169" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="B169" s="1"/>
+      <c r="C169" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="D169" s="1"/>
+    </row>
+    <row r="170" spans="1:4" ht="30" customHeight="1">
+      <c r="A170" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C170" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="D170" s="1" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" ht="30" customHeight="1">
+      <c r="A171" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="B171" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C171" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D171" s="1" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" ht="30" customHeight="1">
+      <c r="A172" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="B172" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="C172" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="D172" s="1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" ht="30" customHeight="1">
+      <c r="A173" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="B173" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C173" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="D173" s="1" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4" ht="30" customHeight="1">
+      <c r="A174" s="30"/>
+      <c r="B174" s="31"/>
+    </row>
+    <row r="175" spans="1:4" ht="30" customHeight="1">
+      <c r="A175" s="26" t="s">
+        <v>263</v>
+      </c>
+      <c r="B175" s="29"/>
+      <c r="C175" s="29"/>
+      <c r="D175" s="27"/>
+    </row>
+    <row r="176" spans="1:4" ht="30" customHeight="1">
+      <c r="A176" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="B176" s="28" t="s">
+        <v>151</v>
+      </c>
+      <c r="C176" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="D176" s="28" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" ht="30" customHeight="1">
+      <c r="A177" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="B177" s="1"/>
+      <c r="C177" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="D177" s="1"/>
+    </row>
+    <row r="178" spans="1:4" ht="30" customHeight="1">
+      <c r="A178" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="B178" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C178" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="D178" s="1" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" ht="30" customHeight="1">
+      <c r="A179" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="B179" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C179" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D179" s="1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4" ht="30" customHeight="1">
+      <c r="A180" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B180" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C180" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="D180" s="1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4" ht="30" customHeight="1">
+      <c r="A181" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B181" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C181" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="D181" s="1" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" ht="30" customHeight="1"/>
+    <row r="183" spans="1:4" ht="30" customHeight="1">
+      <c r="A183" s="14" t="s">
+        <v>255</v>
+      </c>
+      <c r="B183" s="16"/>
+    </row>
+    <row r="184" spans="1:4" ht="30" customHeight="1">
+      <c r="A184" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="B184" s="28" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4" ht="30" customHeight="1">
+      <c r="A185" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="B185" s="1"/>
+    </row>
+    <row r="186" spans="1:4" ht="30" customHeight="1">
+      <c r="A186" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="B186" s="1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" ht="30" customHeight="1">
+      <c r="A187" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B187" s="1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" ht="30" customHeight="1">
+      <c r="A188" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="B188" s="1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4" ht="30" customHeight="1">
+      <c r="A189" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="B189" s="1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4" ht="30" customHeight="1">
+      <c r="A190" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="B190" s="1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" ht="30" customHeight="1"/>
+    <row r="192" spans="1:4" ht="30" customHeight="1"/>
     <row r="193" ht="30" customHeight="1"/>
     <row r="194" ht="30" customHeight="1"/>
     <row r="195" ht="30" customHeight="1"/>
@@ -7218,7 +8472,10 @@
     <row r="240" ht="30" customHeight="1"/>
     <row r="241" ht="30" customHeight="1"/>
   </sheetData>
-  <mergeCells count="33">
+  <mergeCells count="36">
+    <mergeCell ref="A167:D167"/>
+    <mergeCell ref="A175:D175"/>
+    <mergeCell ref="A183:B183"/>
     <mergeCell ref="B62:D62"/>
     <mergeCell ref="B77:D77"/>
     <mergeCell ref="B2:D2"/>
@@ -7277,7 +8534,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="30" customHeight="1">
       <c r="A1" s="13" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="B1" s="8" t="s">
         <v>2</v>
@@ -7293,32 +8550,32 @@
     </row>
     <row r="3" spans="1:11" ht="30" customHeight="1">
       <c r="A3" s="4" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="B3" s="4"/>
     </row>
     <row r="4" spans="1:11" ht="30" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="30" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="30" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="30" customHeight="1">
@@ -7327,19 +8584,19 @@
     </row>
     <row r="8" spans="1:11" ht="30" customHeight="1">
       <c r="A8" s="13" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="B8" s="8" t="s">
         <v>2</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="E8" s="8" t="s">
         <v>2</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="H8" s="8" t="s">
         <v>2</v>
@@ -7367,127 +8624,127 @@
     </row>
     <row r="10" spans="1:11" ht="30" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="B10" s="4"/>
       <c r="D10" s="4" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="E10" s="4"/>
       <c r="G10" s="4" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="H10" s="4"/>
     </row>
     <row r="11" spans="1:11" ht="30" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="30" customHeight="1">
       <c r="A12" s="4" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="30" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>32</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="30" customHeight="1">
       <c r="A14" s="4" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="B14" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="G14" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="D14" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>114</v>
-      </c>
       <c r="H14" s="4" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="30" customHeight="1">
       <c r="G15" s="4" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="30" customHeight="1">
       <c r="A16" s="13" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="B16" s="8" t="s">
         <v>2</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="E16" s="8" t="s">
         <v>2</v>
       </c>
       <c r="G16" s="13" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="H16" s="8" t="s">
         <v>2</v>
       </c>
       <c r="J16" s="13" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="K16" s="8" t="s">
         <v>2</v>
@@ -7521,137 +8778,137 @@
     </row>
     <row r="18" spans="1:11" ht="30" customHeight="1">
       <c r="A18" s="4" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="B18" s="4"/>
       <c r="D18" s="4" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="E18" s="4"/>
       <c r="G18" s="4" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="H18" s="4"/>
       <c r="J18" s="4" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="K18" s="4"/>
     </row>
     <row r="19" spans="1:11" ht="30" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="30" customHeight="1">
       <c r="A20" s="4" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="30" customHeight="1">
       <c r="A21" s="4" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="K21" s="4" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="30" customHeight="1">
       <c r="A22" s="4" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="B22" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="J22" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="D22" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="J22" s="4" t="s">
-        <v>114</v>
-      </c>
       <c r="K22" s="4" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="30" customHeight="1">
       <c r="J23" s="4" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="30" customHeight="1">
       <c r="A24" s="13" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="B24" s="8" t="s">
         <v>2</v>
@@ -7667,50 +8924,50 @@
     </row>
     <row r="26" spans="1:11" ht="30" customHeight="1">
       <c r="A26" s="4" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="B26" s="4"/>
     </row>
     <row r="27" spans="1:11" ht="30" customHeight="1">
       <c r="A27" s="4" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="30" customHeight="1">
       <c r="A28" s="4" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="30" customHeight="1">
       <c r="A29" s="4" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="30" customHeight="1"/>
     <row r="31" spans="1:11" ht="30" customHeight="1">
       <c r="A31" s="13" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="B31" s="8" t="s">
         <v>2</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="E31" s="8" t="s">
         <v>2</v>
       </c>
       <c r="G31" s="13" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="H31" s="8" t="s">
         <v>2</v>
@@ -7738,93 +8995,93 @@
     </row>
     <row r="33" spans="1:8" ht="30" customHeight="1">
       <c r="A33" s="4" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="B33" s="4"/>
       <c r="D33" s="4" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="E33" s="4"/>
       <c r="G33" s="4" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="H33" s="4"/>
     </row>
     <row r="34" spans="1:8" ht="30" customHeight="1">
       <c r="A34" s="4" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="30" customHeight="1">
       <c r="A35" s="4" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="30" customHeight="1">
       <c r="A36" s="4" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="30" customHeight="1">
       <c r="A37" s="4" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="H37" s="4" t="s">
         <v>38</v>
@@ -7832,27 +9089,27 @@
     </row>
     <row r="38" spans="1:8" ht="30" customHeight="1">
       <c r="G38" s="4" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="30" customHeight="1">
       <c r="A39" s="13" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="B39" s="8" t="s">
         <v>2</v>
       </c>
       <c r="D39" s="13" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="E39" s="8" t="s">
         <v>2</v>
       </c>
       <c r="G39" s="13" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="H39" s="8" t="s">
         <v>2</v>
@@ -7880,121 +9137,121 @@
     </row>
     <row r="41" spans="1:8" ht="30" customHeight="1">
       <c r="A41" s="4" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="B41" s="4"/>
       <c r="D41" s="4" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="E41" s="4"/>
       <c r="G41" s="4" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="H41" s="4"/>
     </row>
     <row r="42" spans="1:8" ht="30" customHeight="1">
       <c r="A42" s="4" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="30" customHeight="1">
       <c r="A43" s="4" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="30" customHeight="1">
       <c r="A44" s="4" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="30" customHeight="1">
       <c r="A45" s="4" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="B45" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="G45" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="D45" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="E45" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="G45" s="4" t="s">
-        <v>114</v>
-      </c>
       <c r="H45" s="4" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="30" customHeight="1">
       <c r="G46" s="4" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="30" customHeight="1">
       <c r="A47" s="13" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="B47" s="8" t="s">
         <v>2</v>
       </c>
       <c r="D47" s="13" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="E47" s="8" t="s">
         <v>2</v>
       </c>
       <c r="G47" s="13" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="H47" s="8" t="s">
         <v>2</v>
@@ -8022,116 +9279,92 @@
     </row>
     <row r="49" spans="1:8" ht="30" customHeight="1">
       <c r="A49" s="4" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="B49" s="4"/>
       <c r="D49" s="4" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="E49" s="4"/>
       <c r="G49" s="4" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="H49" s="4"/>
     </row>
     <row r="50" spans="1:8" ht="30" customHeight="1">
       <c r="A50" s="4" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="30" customHeight="1">
       <c r="A51" s="4" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>157</v>
+        <v>223</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>157</v>
+        <v>223</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="30" customHeight="1">
-      <c r="A52" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="D52" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="E52" s="4" t="s">
-        <v>158</v>
-      </c>
+      <c r="A52" s="4"/>
+      <c r="B52" s="4"/>
+      <c r="D52" s="4"/>
+      <c r="E52" s="4"/>
       <c r="G52" s="4" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="30" customHeight="1">
-      <c r="A53" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="B53" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="D53" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="E53" s="4" t="s">
-        <v>159</v>
-      </c>
+      <c r="A53" s="4"/>
+      <c r="B53" s="4"/>
+      <c r="D53" s="4"/>
+      <c r="E53" s="4"/>
       <c r="G53" s="4" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="30" customHeight="1">
-      <c r="A54" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="B54" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="D54" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="E54" s="4" t="s">
-        <v>103</v>
-      </c>
+      <c r="A54" s="4"/>
+      <c r="B54" s="4"/>
+      <c r="D54" s="4"/>
+      <c r="E54" s="4"/>
       <c r="G54" s="4" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="30" customHeight="1"/>
@@ -8215,35 +9448,35 @@
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1">
       <c r="A1" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="B1" s="21" t="s">
-        <v>163</v>
-      </c>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
+        <v>213</v>
+      </c>
+      <c r="B1" s="22" t="s">
+        <v>151</v>
+      </c>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
     </row>
     <row r="2" spans="1:5" ht="30" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="23" t="s">
-        <v>168</v>
-      </c>
-      <c r="C2" s="23" t="s">
-        <v>172</v>
+      <c r="B2" s="24" t="s">
+        <v>156</v>
+      </c>
+      <c r="C2" s="24" t="s">
+        <v>160</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>5</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="30" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -8252,7 +9485,7 @@
     </row>
     <row r="4" spans="1:5" ht="30" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -8261,7 +9494,7 @@
     </row>
     <row r="5" spans="1:5" ht="30" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -8270,22 +9503,22 @@
     </row>
     <row r="6" spans="1:5" ht="30" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="C6" s="24" t="s">
-        <v>174</v>
+        <v>161</v>
+      </c>
+      <c r="C6" s="25" t="s">
+        <v>162</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="E6" s="1"/>
     </row>
     <row r="7" spans="1:5" ht="30" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -8294,52 +9527,52 @@
     </row>
     <row r="8" spans="1:5" ht="30" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="30" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="B10" s="21" t="s">
-        <v>163</v>
-      </c>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
+        <v>214</v>
+      </c>
+      <c r="B10" s="22" t="s">
+        <v>151</v>
+      </c>
+      <c r="C10" s="22"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="22"/>
     </row>
     <row r="11" spans="1:5" ht="30" customHeight="1">
       <c r="A11" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="23" t="s">
-        <v>168</v>
-      </c>
-      <c r="C11" s="23" t="s">
-        <v>172</v>
+      <c r="B11" s="24" t="s">
+        <v>156</v>
+      </c>
+      <c r="C11" s="24" t="s">
+        <v>160</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>5</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="30" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -8348,7 +9581,7 @@
     </row>
     <row r="13" spans="1:5" ht="30" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -8357,7 +9590,7 @@
     </row>
     <row r="14" spans="1:5" ht="30" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -8366,24 +9599,24 @@
     </row>
     <row r="15" spans="1:5" ht="30" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="C15" s="24" t="s">
-        <v>174</v>
+        <v>161</v>
+      </c>
+      <c r="C15" s="25" t="s">
+        <v>162</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="30" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -8392,19 +9625,19 @@
     </row>
     <row r="17" spans="1:5" ht="30" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="30" customHeight="1"/>

--- a/internal_doc/05.测试设计/story/事务支持RC隔离级别/测试场景.xlsx
+++ b/internal_doc/05.测试设计/story/事务支持RC隔离级别/测试场景.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="954" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="965" uniqueCount="265">
   <si>
     <t>操作步骤</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4893,6 +4893,88 @@
   </si>
   <si>
     <t>场景13：读并发与删除并发(RC隔离级别)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>3.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>事务</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>使用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>select</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>索引读</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>记录读记录</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>R1</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -6258,10 +6340,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D241"/>
+  <dimension ref="A1:F241"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="4" width="30.625" customWidth="1"/>
+    <col min="1" max="6" width="30.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="30" customHeight="1">
@@ -8116,7 +8198,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="161" spans="1:4" ht="30" customHeight="1">
+    <row r="161" spans="1:6" ht="30" customHeight="1">
       <c r="A161" s="2" t="s">
         <v>62</v>
       </c>
@@ -8130,7 +8212,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="162" spans="1:4" ht="30" customHeight="1">
+    <row r="162" spans="1:6" ht="30" customHeight="1">
       <c r="A162" s="7" t="s">
         <v>63</v>
       </c>
@@ -8142,7 +8224,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="163" spans="1:4" ht="30" customHeight="1">
+    <row r="163" spans="1:6" ht="30" customHeight="1">
       <c r="A163" s="7" t="s">
         <v>43</v>
       </c>
@@ -8154,7 +8236,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="164" spans="1:4" ht="30" customHeight="1">
+    <row r="164" spans="1:6" ht="30" customHeight="1">
       <c r="A164" s="7" t="s">
         <v>64</v>
       </c>
@@ -8166,7 +8248,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="165" spans="1:4" ht="30" customHeight="1">
+    <row r="165" spans="1:6" ht="30" customHeight="1">
       <c r="A165" s="7" t="s">
         <v>65</v>
       </c>
@@ -8178,8 +8260,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="166" spans="1:4" ht="30" customHeight="1"/>
-    <row r="167" spans="1:4" ht="30" customHeight="1">
+    <row r="166" spans="1:6" ht="30" customHeight="1"/>
+    <row r="167" spans="1:6" ht="30" customHeight="1">
       <c r="A167" s="26" t="s">
         <v>241</v>
       </c>
@@ -8187,7 +8269,7 @@
       <c r="C167" s="29"/>
       <c r="D167" s="27"/>
     </row>
-    <row r="168" spans="1:4" ht="30" customHeight="1">
+    <row r="168" spans="1:6" ht="30" customHeight="1">
       <c r="A168" s="24" t="s">
         <v>0</v>
       </c>
@@ -8201,7 +8283,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="169" spans="1:4" ht="30" customHeight="1">
+    <row r="169" spans="1:6" ht="30" customHeight="1">
       <c r="A169" s="2" t="s">
         <v>235</v>
       </c>
@@ -8211,7 +8293,7 @@
       </c>
       <c r="D169" s="1"/>
     </row>
-    <row r="170" spans="1:4" ht="30" customHeight="1">
+    <row r="170" spans="1:6" ht="30" customHeight="1">
       <c r="A170" s="2" t="s">
         <v>238</v>
       </c>
@@ -8225,7 +8307,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="171" spans="1:4" ht="30" customHeight="1">
+    <row r="171" spans="1:6" ht="30" customHeight="1">
       <c r="A171" s="2" t="s">
         <v>237</v>
       </c>
@@ -8239,7 +8321,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="172" spans="1:4" ht="30" customHeight="1">
+    <row r="172" spans="1:6" ht="30" customHeight="1">
       <c r="A172" s="2" t="s">
         <v>249</v>
       </c>
@@ -8253,7 +8335,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="173" spans="1:4" ht="30" customHeight="1">
+    <row r="173" spans="1:6" ht="30" customHeight="1">
       <c r="A173" s="2" t="s">
         <v>250</v>
       </c>
@@ -8267,11 +8349,11 @@
         <v>243</v>
       </c>
     </row>
-    <row r="174" spans="1:4" ht="30" customHeight="1">
+    <row r="174" spans="1:6" ht="30" customHeight="1">
       <c r="A174" s="30"/>
       <c r="B174" s="31"/>
     </row>
-    <row r="175" spans="1:4" ht="30" customHeight="1">
+    <row r="175" spans="1:6" ht="30" customHeight="1">
       <c r="A175" s="26" t="s">
         <v>263</v>
       </c>
@@ -8279,7 +8361,7 @@
       <c r="C175" s="29"/>
       <c r="D175" s="27"/>
     </row>
-    <row r="176" spans="1:4" ht="30" customHeight="1">
+    <row r="176" spans="1:6" ht="30" customHeight="1">
       <c r="A176" s="24" t="s">
         <v>0</v>
       </c>
@@ -8292,8 +8374,14 @@
       <c r="D176" s="28" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="177" spans="1:4" ht="30" customHeight="1">
+      <c r="E176" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="F176" s="28" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" ht="30" customHeight="1">
       <c r="A177" s="2" t="s">
         <v>235</v>
       </c>
@@ -8302,8 +8390,12 @@
         <v>254</v>
       </c>
       <c r="D177" s="1"/>
-    </row>
-    <row r="178" spans="1:4" ht="30" customHeight="1">
+      <c r="E177" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="F177" s="1"/>
+    </row>
+    <row r="178" spans="1:6" ht="30" customHeight="1">
       <c r="A178" s="2" t="s">
         <v>238</v>
       </c>
@@ -8314,10 +8406,16 @@
         <v>240</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="179" spans="1:4" ht="30" customHeight="1">
+        <v>171</v>
+      </c>
+      <c r="E178" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="F178" s="1" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" ht="30" customHeight="1">
       <c r="A179" s="2" t="s">
         <v>237</v>
       </c>
@@ -8330,8 +8428,14 @@
       <c r="D179" s="1" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="180" spans="1:4" ht="30" customHeight="1">
+      <c r="E179" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="F179" s="1" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" ht="30" customHeight="1">
       <c r="A180" s="2" t="s">
         <v>247</v>
       </c>
@@ -8344,8 +8448,14 @@
       <c r="D180" s="1" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="181" spans="1:4" ht="30" customHeight="1">
+      <c r="E180" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="F180" s="1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" ht="30" customHeight="1">
       <c r="A181" s="2" t="s">
         <v>251</v>
       </c>
@@ -8358,15 +8468,21 @@
       <c r="D181" s="1" t="s">
         <v>253</v>
       </c>
-    </row>
-    <row r="182" spans="1:4" ht="30" customHeight="1"/>
-    <row r="183" spans="1:4" ht="30" customHeight="1">
+      <c r="E181" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="F181" s="1" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" ht="30" customHeight="1"/>
+    <row r="183" spans="1:6" ht="30" customHeight="1">
       <c r="A183" s="14" t="s">
         <v>255</v>
       </c>
       <c r="B183" s="16"/>
     </row>
-    <row r="184" spans="1:4" ht="30" customHeight="1">
+    <row r="184" spans="1:6" ht="30" customHeight="1">
       <c r="A184" s="24" t="s">
         <v>0</v>
       </c>
@@ -8374,13 +8490,13 @@
         <v>151</v>
       </c>
     </row>
-    <row r="185" spans="1:4" ht="30" customHeight="1">
+    <row r="185" spans="1:6" ht="30" customHeight="1">
       <c r="A185" s="2" t="s">
         <v>261</v>
       </c>
       <c r="B185" s="1"/>
     </row>
-    <row r="186" spans="1:4" ht="30" customHeight="1">
+    <row r="186" spans="1:6" ht="30" customHeight="1">
       <c r="A186" s="2" t="s">
         <v>256</v>
       </c>
@@ -8388,7 +8504,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="187" spans="1:4" ht="30" customHeight="1">
+    <row r="187" spans="1:6" ht="30" customHeight="1">
       <c r="A187" s="2" t="s">
         <v>257</v>
       </c>
@@ -8396,7 +8512,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="188" spans="1:4" ht="30" customHeight="1">
+    <row r="188" spans="1:6" ht="30" customHeight="1">
       <c r="A188" s="2" t="s">
         <v>258</v>
       </c>
@@ -8404,7 +8520,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="189" spans="1:4" ht="30" customHeight="1">
+    <row r="189" spans="1:6" ht="30" customHeight="1">
       <c r="A189" s="2" t="s">
         <v>259</v>
       </c>
@@ -8412,7 +8528,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="190" spans="1:4" ht="30" customHeight="1">
+    <row r="190" spans="1:6" ht="30" customHeight="1">
       <c r="A190" s="1" t="s">
         <v>260</v>
       </c>
@@ -8420,8 +8536,8 @@
         <v>262</v>
       </c>
     </row>
-    <row r="191" spans="1:4" ht="30" customHeight="1"/>
-    <row r="192" spans="1:4" ht="30" customHeight="1"/>
+    <row r="191" spans="1:6" ht="30" customHeight="1"/>
+    <row r="192" spans="1:6" ht="30" customHeight="1"/>
     <row r="193" ht="30" customHeight="1"/>
     <row r="194" ht="30" customHeight="1"/>
     <row r="195" ht="30" customHeight="1"/>

--- a/internal_doc/05.测试设计/story/事务支持RC隔离级别/测试场景.xlsx
+++ b/internal_doc/05.测试设计/story/事务支持RC隔离级别/测试场景.xlsx
@@ -8282,6 +8282,12 @@
       <c r="D168" s="28" t="s">
         <v>151</v>
       </c>
+      <c r="E168" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="F168" s="28" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="169" spans="1:6" ht="30" customHeight="1">
       <c r="A169" s="2" t="s">
@@ -8292,6 +8298,10 @@
         <v>239</v>
       </c>
       <c r="D169" s="1"/>
+      <c r="E169" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="F169" s="1"/>
     </row>
     <row r="170" spans="1:6" ht="30" customHeight="1">
       <c r="A170" s="2" t="s">
@@ -8306,6 +8316,12 @@
       <c r="D170" s="1" t="s">
         <v>236</v>
       </c>
+      <c r="E170" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="F170" s="1" t="s">
+        <v>171</v>
+      </c>
     </row>
     <row r="171" spans="1:6" ht="30" customHeight="1">
       <c r="A171" s="2" t="s">
@@ -8318,7 +8334,13 @@
         <v>245</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>236</v>
+        <v>162</v>
+      </c>
+      <c r="E171" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="F171" s="1" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="172" spans="1:6" ht="30" customHeight="1">
@@ -8334,6 +8356,12 @@
       <c r="D172" s="1" t="s">
         <v>162</v>
       </c>
+      <c r="E172" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="F172" s="1" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="173" spans="1:6" ht="30" customHeight="1">
       <c r="A173" s="2" t="s">
@@ -8348,6 +8376,12 @@
       <c r="D173" s="1" t="s">
         <v>243</v>
       </c>
+      <c r="E173" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="F173" s="1" t="s">
+        <v>253</v>
+      </c>
     </row>
     <row r="174" spans="1:6" ht="30" customHeight="1">
       <c r="A174" s="30"/>
@@ -8374,14 +8408,8 @@
       <c r="D176" s="28" t="s">
         <v>151</v>
       </c>
-      <c r="E176" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="F176" s="28" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="177" spans="1:6" ht="30" customHeight="1">
+    </row>
+    <row r="177" spans="1:4" ht="30" customHeight="1">
       <c r="A177" s="2" t="s">
         <v>235</v>
       </c>
@@ -8390,12 +8418,8 @@
         <v>254</v>
       </c>
       <c r="D177" s="1"/>
-      <c r="E177" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="F177" s="1"/>
-    </row>
-    <row r="178" spans="1:6" ht="30" customHeight="1">
+    </row>
+    <row r="178" spans="1:4" ht="30" customHeight="1">
       <c r="A178" s="2" t="s">
         <v>238</v>
       </c>
@@ -8408,14 +8432,8 @@
       <c r="D178" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="E178" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="F178" s="1" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="179" spans="1:6" ht="30" customHeight="1">
+    </row>
+    <row r="179" spans="1:4" ht="30" customHeight="1">
       <c r="A179" s="2" t="s">
         <v>237</v>
       </c>
@@ -8428,14 +8446,8 @@
       <c r="D179" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="E179" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="F179" s="1" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="180" spans="1:6" ht="30" customHeight="1">
+    </row>
+    <row r="180" spans="1:4" ht="30" customHeight="1">
       <c r="A180" s="2" t="s">
         <v>247</v>
       </c>
@@ -8448,14 +8460,8 @@
       <c r="D180" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="E180" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="F180" s="1" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="181" spans="1:6" ht="30" customHeight="1">
+    </row>
+    <row r="181" spans="1:4" ht="30" customHeight="1">
       <c r="A181" s="2" t="s">
         <v>251</v>
       </c>
@@ -8468,21 +8474,15 @@
       <c r="D181" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="E181" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="F181" s="1" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="182" spans="1:6" ht="30" customHeight="1"/>
-    <row r="183" spans="1:6" ht="30" customHeight="1">
+    </row>
+    <row r="182" spans="1:4" ht="30" customHeight="1"/>
+    <row r="183" spans="1:4" ht="30" customHeight="1">
       <c r="A183" s="14" t="s">
         <v>255</v>
       </c>
       <c r="B183" s="16"/>
     </row>
-    <row r="184" spans="1:6" ht="30" customHeight="1">
+    <row r="184" spans="1:4" ht="30" customHeight="1">
       <c r="A184" s="24" t="s">
         <v>0</v>
       </c>
@@ -8490,13 +8490,13 @@
         <v>151</v>
       </c>
     </row>
-    <row r="185" spans="1:6" ht="30" customHeight="1">
+    <row r="185" spans="1:4" ht="30" customHeight="1">
       <c r="A185" s="2" t="s">
         <v>261</v>
       </c>
       <c r="B185" s="1"/>
     </row>
-    <row r="186" spans="1:6" ht="30" customHeight="1">
+    <row r="186" spans="1:4" ht="30" customHeight="1">
       <c r="A186" s="2" t="s">
         <v>256</v>
       </c>
@@ -8504,7 +8504,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="187" spans="1:6" ht="30" customHeight="1">
+    <row r="187" spans="1:4" ht="30" customHeight="1">
       <c r="A187" s="2" t="s">
         <v>257</v>
       </c>
@@ -8512,7 +8512,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="188" spans="1:6" ht="30" customHeight="1">
+    <row r="188" spans="1:4" ht="30" customHeight="1">
       <c r="A188" s="2" t="s">
         <v>258</v>
       </c>
@@ -8520,7 +8520,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="189" spans="1:6" ht="30" customHeight="1">
+    <row r="189" spans="1:4" ht="30" customHeight="1">
       <c r="A189" s="2" t="s">
         <v>259</v>
       </c>
@@ -8528,7 +8528,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="190" spans="1:6" ht="30" customHeight="1">
+    <row r="190" spans="1:4" ht="30" customHeight="1">
       <c r="A190" s="1" t="s">
         <v>260</v>
       </c>
@@ -8536,8 +8536,8 @@
         <v>262</v>
       </c>
     </row>
-    <row r="191" spans="1:6" ht="30" customHeight="1"/>
-    <row r="192" spans="1:6" ht="30" customHeight="1"/>
+    <row r="191" spans="1:4" ht="30" customHeight="1"/>
+    <row r="192" spans="1:4" ht="30" customHeight="1"/>
     <row r="193" ht="30" customHeight="1"/>
     <row r="194" ht="30" customHeight="1"/>
     <row r="195" ht="30" customHeight="1"/>
